--- a/tables_filled/c433ba8b-76d9-4231-b916-8013f9f7b4da.xlsx
+++ b/tables_filled/c433ba8b-76d9-4231-b916-8013f9f7b4da.xlsx
@@ -14,6 +14,1081 @@
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="142">
+  <si>
+    <t>Bewerberbogen</t>
+  </si>
+  <si>
+    <t>Name des Bewerbers</t>
+  </si>
+  <si>
+    <t>Nr.</t>
+  </si>
+  <si>
+    <t>Frage/Kriterium</t>
+  </si>
+  <si>
+    <t>Hinweise zur Antwort</t>
+  </si>
+  <si>
+    <t>Antwort des Unternehmens</t>
+  </si>
+  <si>
+    <t>Teil I: Allgemeine Angaben</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Angaben zur Art der Teilnahme</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ich bin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Bewerber </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>und beteilige mich am Teilnahmewettbewerb.</t>
+    </r>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ich bin </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">vertretungsberechtigtes Mitglied einer Bewerbergemeinschaft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>und beteilige mich im Namen dieser am  Teilnahmewettbewerb.</t>
+    </r>
+  </si>
+  <si>
+    <t>Name der Bewerbergemeinschaft und Ihr Name</t>
+  </si>
+  <si>
+    <t>1.1.3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ich bin weiteres, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nicht vertretungsberechtigtes Mitglied einer Bewerbergemeinschaft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, das sich am Teilnahmewettbewerb  beteiligt.</t>
+    </r>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ich bin ein </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>anderes Unternehmen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, dessen Kapazität im Hinblick auf die wirtschaftliche und finanzielle Leistungsfähigkeit in Anspruch genommen werden soll (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Eignungsleihe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>Name des Bewerbers und Ihr Name</t>
+  </si>
+  <si>
+    <t>1.1.5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ich bin ein </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>anderes Unternehmen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, dem im Wege der Unterauftragsvergabe ein Teil des Auftrags gegeben werden soll.</t>
+    </r>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Angaben zur Verwendung einer Einheitlichen Europäischen Eigenerklärung (EEE)</t>
+  </si>
+  <si>
+    <t>[§ 50 VgV]</t>
+  </si>
+  <si>
+    <t>1.2.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Das Unternehmen hat eine </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Einheitliche Europäische Eigenerklärung (EEE) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>als vorläufigen Nachweis ausgefüllt und als Anlage hochgeladen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ja: / nein:   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x</t>
+    </r>
+  </si>
+  <si>
+    <t>ja:</t>
+  </si>
+  <si>
+    <t>nein:</t>
+  </si>
+  <si>
+    <t>Teil II: Angaben zum Unternehmen</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Angaben zur Identität des Unternehmens</t>
+  </si>
+  <si>
+    <t>2.1.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Name:</t>
+    </r>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>Postanschrift:</t>
+  </si>
+  <si>
+    <t>2.1.3</t>
+  </si>
+  <si>
+    <t>Ansprechpartner</t>
+  </si>
+  <si>
+    <t>2.1.4</t>
+  </si>
+  <si>
+    <t>Telefon:</t>
+  </si>
+  <si>
+    <t>2.1.5</t>
+  </si>
+  <si>
+    <t>E-Mail:</t>
+  </si>
+  <si>
+    <t>2.1.6</t>
+  </si>
+  <si>
+    <r>
+      <t>Web-Adresse (URL)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>2.1.7</t>
+  </si>
+  <si>
+    <t>Gründungsjahr des Unternehmens</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Angaben zu Vertretern des Unternehmens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Bitte Name(n) und Anschrift(en) der Person(en), die zur Vertretung des Unternehmens in diesem Vergabeverfahren ermächtigt ist (sind) angeben:</t>
+  </si>
+  <si>
+    <t>2.2.1</t>
+  </si>
+  <si>
+    <t>Vorname, Name</t>
+  </si>
+  <si>
+    <t>2.2.2</t>
+  </si>
+  <si>
+    <t>Position/Beauftragt in seiner/ihrer Eigenschaft als:</t>
+  </si>
+  <si>
+    <t>2.2.3</t>
+  </si>
+  <si>
+    <t>2.2.4</t>
+  </si>
+  <si>
+    <t>2.2.5</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Angaben zur Inanspruchnahme der Kapazitäten anderer Unternehmen  (Eignungsleihe)</t>
+  </si>
+  <si>
+    <t>[§ 47 VgV]</t>
+  </si>
+  <si>
+    <t>2.3.1</t>
+  </si>
+  <si>
+    <t>Nimmt das Unternehmen zur Erfüllung der Eignungskriterien die Kapazitäten anderer Unternehmen in Anspruch?</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Angaben zur Vergabe von Unteraufträgen</t>
+  </si>
+  <si>
+    <t>[§ 36 VgV]</t>
+  </si>
+  <si>
+    <t>2.4.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Beabsichtigt das Unternehmen, einen Teil des Auftrags im Wege der Unterauftragsvergabe an Dritte weiterzuvergeben?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Falls ja</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, nennen Sie bitte die Namen der vorgeschlagenen  Unterauftragnehmer:</t>
+    </r>
+  </si>
+  <si>
+    <t>Teil III: Eignungskriterien</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Befähigung zur Berufsausübung
+</t>
+  </si>
+  <si>
+    <t>[§ 44 VgV]</t>
+  </si>
+  <si>
+    <t>3.1.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ist das Unternehmen in den einschlägigen Berufs- oder Handelsregistern  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">seines  Niederlassungsmitgliedstaates eingetragen?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Falls ja, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>geben Sie bitte das Berufs- oder Handelsregister mit Eintragungsort und -nummer an.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.1.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ist der Besitz einer bestimmten </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Berechtigung </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">oder die </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Mitgliedschaft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">in einer bestimmten Organisation erforderlich, um die betreffende Dienstleistung im Niederlassungsstaat des Unternehmens erbringen zu können?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Falls ja</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, geben Sie bitte an, welche Berechtigung oder Mitgliedschaft verlangt wird und ob das Unternehmen diese Voraussetzung erfüllt.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaftliche und finanzielle Leistungsfähigkeit
+</t>
+  </si>
+  <si>
+    <t>[§ 45 VgV]</t>
+  </si>
+  <si>
+    <t>3.2.1</t>
+  </si>
+  <si>
+    <r>
+      <t>Der J</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ahresumsatz </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>des Unternehmens betrug:</t>
+    </r>
+  </si>
+  <si>
+    <t>Jahr: 2022 Umsatz: … EUR</t>
+  </si>
+  <si>
+    <t>Jahr: 2023 Umsatz: … EUR</t>
+  </si>
+  <si>
+    <t>Jahr: 2024 Umsatz: … EUR</t>
+  </si>
+  <si>
+    <t>3.2.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hat das Unternehmen eine </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Berufshaftpflichtversicherung </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">entsprechend den Forderungen der Auftragsbekanntmachung abgeschlossen?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Falls ja</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: Eine entsprechende Berufshaftpflichtversicherung wird nachgewiesen:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Falls nein</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Das Unternehmen erklärt, im Auftragsfall eine entsprechende  Berufshaftpflichtversicherung  abzuschließen und bringt eine entsprechende Erklärung der Versicherung bei.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Bitte mit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ja </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">oder </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Nein </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">antworten.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Falls ja </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: Der Versicherungsnachweis ist als Anlage hochzuladen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Falls nein:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Eine entsprechende Erklärung der Versicherung ist als Anlage hochzuladen.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technische und berufliche Leistungsfähigkeit
+</t>
+  </si>
+  <si>
+    <t>[§ 46 VgV]</t>
+  </si>
+  <si>
+    <t>3.3.1</t>
+  </si>
+  <si>
+    <t>Anzahl der Mitarbeiter in den letzten drei Jahren</t>
+  </si>
+  <si>
+    <t>Geschäftsleitung</t>
+  </si>
+  <si>
+    <t>Jahr 2022</t>
+  </si>
+  <si>
+    <t>Jahr 2023</t>
+  </si>
+  <si>
+    <t>Jahr 2024</t>
+  </si>
+  <si>
+    <t>Fachpersonal</t>
+  </si>
+  <si>
+    <t>Sonstige</t>
+  </si>
+  <si>
+    <t>Gesamtzahl</t>
+  </si>
+  <si>
+    <t>3.3.2</t>
+  </si>
+  <si>
+    <t>Technische Ausstattung</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eine Aufstellung ist als </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anlage</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> beizufügen</t>
+    </r>
+  </si>
+  <si>
+    <t>Versionsnummer der für die Verarbeitung der Vermessungsdaten verwendeten Software (HHK GEOgraf)</t>
+  </si>
+  <si>
+    <t>Messgeräte</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Eine Aufstellung ist als </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anlage</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> beizufügen</t>
+    </r>
+  </si>
+  <si>
+    <t>3.3.3</t>
+  </si>
+  <si>
+    <t>Qualitätssicherung</t>
+  </si>
+  <si>
+    <t>Eine aktuelle Zertifizierung liegt vor</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ein Nachweis ist als </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anlage</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> beizufügen</t>
+    </r>
+  </si>
+  <si>
+    <t>Ein an die Kriterien der DIN/ISO 9001 angelehntes firmeneigenes Qualitätsmanagementsystem liegt vor.</t>
+  </si>
+  <si>
+    <t>3.3.4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Das Unternehmen beabsichtigt folgenden Teil des Auftrags als Unterauftrag zu vergeben:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">vorgesehene Unterauftragnehmer und deren Leistungsbereich sind anzugeben
+</t>
+  </si>
+  <si>
+    <t>3.3.5</t>
+  </si>
+  <si>
+    <t>Für das Projekt vorgesehene Mitarbeiter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Als </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anlage</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sind beizufügen:
+a) ein Organigramm der Projektorganisation
+b) Lebensläufe, Nachweise der Berufszulassung bzw. der beruflichen Befähigung für die unten angegebenen Personen</t>
+    </r>
+  </si>
+  <si>
+    <t>Büroleitung / Projektleitung</t>
+  </si>
+  <si>
+    <t>Vermesser</t>
+  </si>
+  <si>
+    <t>Teil IV: Referenzen des Bewerbers</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Mind. 3 Referenzen des Bewerbers zu vergleichbaren Projekten der Vermessung, die in den letzten 5 Jahren abgeschlossen oder bearbeitet wurden</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Die Angaben sind durch firmeneigene Referenzbeschreibungen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">zu </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ergänzen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (als pdf-Datei hochladen)</t>
+    </r>
+  </si>
+  <si>
+    <t>4.1.1</t>
+  </si>
+  <si>
+    <t>Referenzprojekt 1</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>Auftraggeber</t>
+  </si>
+  <si>
+    <t>Ansprechpartner / Adresse / Telefon</t>
+  </si>
+  <si>
+    <t>Projektzeitraum (Anfang-Ende)</t>
+  </si>
+  <si>
+    <t>Honorarsumme (netto) 
+(nur bereits erbrachte Leistungen des Bieters)</t>
+  </si>
+  <si>
+    <t>Verantwortlicher Projektleiter/Vermesser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fachtechnische Merkmale des Referenzprojekts </t>
+  </si>
+  <si>
+    <t>Kurzbeschreibung des Auftragsgegenstandes</t>
+  </si>
+  <si>
+    <t>Anzahl aufgemessener Schächte</t>
+  </si>
+  <si>
+    <t>Sonstige Besonderheiten</t>
+  </si>
+  <si>
+    <t>4.1.2</t>
+  </si>
+  <si>
+    <t>Referenzprojekt 2</t>
+  </si>
+  <si>
+    <t>4.1.3</t>
+  </si>
+  <si>
+    <t>Referenzprojekt 3</t>
+  </si>
+  <si>
+    <t>4.1.4</t>
+  </si>
+  <si>
+    <t>weitere Referenzprojekt</t>
+  </si>
+  <si>
+    <t>Anzahl der weiteren Referenzprojekte</t>
+  </si>
+  <si>
+    <t>Teil V: Abschlusserklärungen</t>
+  </si>
+  <si>
+    <t>Das Unternehmen erklärt förmlich, dass die von ihm angegebenen Informationen genau und korrekt sind und es sich der Konsequenzen einer schwerwiegenden Täuschung bewusst ist.
+Das Unternehmen erklärt förmlich, dass es in der Lage ist, auf Anfrage unverzüglich die Bescheinigungen und anderen genannten dokumentarischen Nachweise beizubringen, außer wenn der öffentliche Auftraggeber über die Möglichkeit verfügt, die betreffenden zusätzlichen Unterlagen direkt über eine gebührenfreie nationale Datenbank in einem Mitgliedsstaat abzurufen.
+Das Unternehmen stimmt förmlich zu, dass der Öffentliche Auftraggeber Zugang zu den Unterlagen erhält, mit denen die Informationen belegt werden, die das Unternehmen diesem Teilnahmeantrag für die Zwecke dieses Vergabeverfahrens angegeben haben.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1490,11 +2565,7 @@
           <t>Name des Bewerbers</t>
         </is>
       </c>
-      <c r="D3" s="93" t="inlineStr">
-        <is>
-          <t>Hansa Planungsgruppe GmbH</t>
-        </is>
-      </c>
+      <c r="D3" s="93" t="n"/>
       <c r="E3" s="116" t="n"/>
       <c r="F3" s="116" t="n"/>
       <c r="G3" s="116" t="n"/>
@@ -1755,11 +2826,7 @@
           <t>ja:</t>
         </is>
       </c>
-      <c r="E13" s="89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="E13" s="89" t="n"/>
       <c r="F13" s="116" t="n"/>
       <c r="G13" s="117" t="n"/>
       <c r="H13" s="30" t="inlineStr">
@@ -2030,7 +3097,7 @@
       <c r="C24" s="114" t="n"/>
       <c r="D24" s="93" t="inlineStr">
         <is>
-          <t>Anna-Lena Krüger</t>
+          <t>Dipl.-Ing. Anna-Lena Krüger</t>
         </is>
       </c>
       <c r="E24" s="116" t="n"/>
@@ -2203,7 +3270,7 @@
       </c>
       <c r="I30" s="89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J30" s="116" t="n"/>
@@ -2260,7 +3327,7 @@
       </c>
       <c r="E32" s="89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F32" s="116" t="n"/>
@@ -2344,7 +3411,7 @@
       </c>
       <c r="E35" s="89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>HRB 154287, Amtsgericht Hamburg</t>
         </is>
       </c>
       <c r="F35" s="116" t="n"/>
@@ -2383,7 +3450,7 @@
       </c>
       <c r="E36" s="89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Hamburgische Ingenieurkammer-Bau; Architektenkammer Hamburg</t>
         </is>
       </c>
       <c r="F36" s="116" t="n"/>
@@ -2520,11 +3587,7 @@
           <t>ja:</t>
         </is>
       </c>
-      <c r="E41" s="89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="E41" s="89" t="n"/>
       <c r="F41" s="116" t="n"/>
       <c r="G41" s="117" t="n"/>
       <c r="H41" s="30" t="inlineStr">
@@ -2598,7 +3661,11 @@
           <t>Jahr 2022</t>
         </is>
       </c>
-      <c r="D44" s="88" t="n"/>
+      <c r="D44" s="88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E44" s="116" t="n"/>
       <c r="F44" s="116" t="n"/>
       <c r="G44" s="116" t="n"/>
@@ -2616,7 +3683,11 @@
           <t>Jahr 2023</t>
         </is>
       </c>
-      <c r="D45" s="88" t="n"/>
+      <c r="D45" s="88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E45" s="116" t="n"/>
       <c r="F45" s="116" t="n"/>
       <c r="G45" s="116" t="n"/>
@@ -2660,7 +3731,11 @@
           <t>Jahr 2022</t>
         </is>
       </c>
-      <c r="D47" s="88" t="n"/>
+      <c r="D47" s="88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="E47" s="116" t="n"/>
       <c r="F47" s="116" t="n"/>
       <c r="G47" s="116" t="n"/>
@@ -2678,7 +3753,11 @@
           <t>Jahr 2023</t>
         </is>
       </c>
-      <c r="D48" s="88" t="n"/>
+      <c r="D48" s="88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="E48" s="116" t="n"/>
       <c r="F48" s="116" t="n"/>
       <c r="G48" s="116" t="n"/>
@@ -2722,7 +3801,11 @@
           <t>Jahr 2022</t>
         </is>
       </c>
-      <c r="D50" s="88" t="n"/>
+      <c r="D50" s="88" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="E50" s="116" t="n"/>
       <c r="F50" s="116" t="n"/>
       <c r="G50" s="116" t="n"/>
@@ -2740,7 +3823,11 @@
           <t>Jahr 2023</t>
         </is>
       </c>
-      <c r="D51" s="88" t="n"/>
+      <c r="D51" s="88" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="E51" s="116" t="n"/>
       <c r="F51" s="116" t="n"/>
       <c r="G51" s="116" t="n"/>
@@ -2784,7 +3871,11 @@
           <t>Jahr 2022</t>
         </is>
       </c>
-      <c r="D53" s="88" t="n"/>
+      <c r="D53" s="88" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="E53" s="116" t="n"/>
       <c r="F53" s="116" t="n"/>
       <c r="G53" s="116" t="n"/>
@@ -2802,7 +3893,11 @@
           <t>Jahr 2023</t>
         </is>
       </c>
-      <c r="D54" s="88" t="n"/>
+      <c r="D54" s="88" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="E54" s="116" t="n"/>
       <c r="F54" s="116" t="n"/>
       <c r="G54" s="116" t="n"/>
@@ -3035,7 +4130,7 @@
       <c r="C64" s="56" t="n"/>
       <c r="D64" s="88" t="inlineStr">
         <is>
-          <t>M. Sc. Arch. Sophie Reinhardt</t>
+          <t>M. Sc. Arch. Sophie Reinhardt, Dipl.-Ing. (FH) Markus Ebert</t>
         </is>
       </c>
       <c r="E64" s="116" t="n"/>
@@ -3256,7 +4351,7 @@
       <c r="C74" s="114" t="n"/>
       <c r="D74" s="88" t="inlineStr">
         <is>
-          <t>Markus Ebert / Jonas Feldmann</t>
+          <t>Dipl.-Ing. (FH) Markus Ebert</t>
         </is>
       </c>
       <c r="E74" s="116" t="n"/>
@@ -3296,7 +4391,7 @@
       <c r="C76" s="68" t="n"/>
       <c r="D76" s="87" t="inlineStr">
         <is>
-          <t>Umfassende Modernisierung eines bestehenden Schulcampus mit teilweiser Erneuerung der Haustechnik, Fassadensanierung, Dachsanierung, Brandschutzertüchtigung und Schadstoffsanierung.</t>
+          <t>Umfassende Modernisierung eines bestehenden Schulcampus mit teilweiser Erneuerung der Haustechnik, Fassadensanierung, Dachsanierung, Brandschutzertüchtigung, Schadstoffsanierung und Installation von Photovoltaikanlagen.</t>
         </is>
       </c>
       <c r="E76" s="116" t="n"/>
@@ -3336,7 +4431,7 @@
       <c r="C78" s="72" t="n"/>
       <c r="D78" s="88" t="inlineStr">
         <is>
-          <t>Schadstoffsanierung mit Schwarzbereich, Brandschutzmaßnahmen, Strangsanierung, Ausführung im laufenden Schulbetrieb</t>
+          <t>Ausführung in Bauabschnitten bei laufendem Schulbetrieb, Schadstoffsanierung mit Schwarzbereich, Brandschutzmaßnahmen, Strangsanierung</t>
         </is>
       </c>
       <c r="E78" s="116" t="n"/>
@@ -3491,7 +4586,7 @@
       <c r="C85" s="114" t="n"/>
       <c r="D85" s="88" t="inlineStr">
         <is>
-          <t>Sophie Reinhardt</t>
+          <t>M. Sc. Arch. Sophie Reinhardt</t>
         </is>
       </c>
       <c r="E85" s="116" t="n"/>
@@ -3531,7 +4626,7 @@
       <c r="C87" s="68" t="n"/>
       <c r="D87" s="87" t="inlineStr">
         <is>
-          <t>Modernisierung einer Wohnanlage aus den 1970er Jahren inkl. Fassadensanierung, Erneuerung der Steigleitungen, Brandschutzertüchtigung, Barrierefreiheit.</t>
+          <t>Modernisierung einer Wohnanlage aus den 1970er Jahren, inkl. Fassadensanierung, Erneuerung der Steigleitungen, Brandschutzertüchtigung, Barrierefreiheit, Sanierung der Gemeinschaftsflächen und Erneuerung der zentralen Heizungs- und Lüftungskomponenten.</t>
         </is>
       </c>
       <c r="E87" s="116" t="n"/>
@@ -3571,7 +4666,7 @@
       <c r="C89" s="72" t="n"/>
       <c r="D89" s="88" t="inlineStr">
         <is>
-          <t>Strangsanierung, Brandschutzmaßnahmen in Schächten, abschnittsweise Arbeiten im bewohnten Zustand</t>
+          <t>Strangsanierung, Brandschutzmaßnahmen, abschnittsweise Arbeiten im bewohnten Gebäude mit provisorischer Versorgung</t>
         </is>
       </c>
       <c r="E89" s="116" t="n"/>
@@ -3659,7 +4754,7 @@
       <c r="C93" s="114" t="n"/>
       <c r="D93" s="88" t="inlineStr">
         <is>
-          <t>Ratzeburger Allee 160, 23538 Lübeck</t>
+          <t>Campus Lübeck, Ratzeburger Allee 160, 23538 Lübeck</t>
         </is>
       </c>
       <c r="E93" s="116" t="n"/>
@@ -3726,7 +4821,7 @@
       <c r="C96" s="114" t="n"/>
       <c r="D96" s="88" t="inlineStr">
         <is>
-          <t>Markus Ebert / Sophie Reinhardt</t>
+          <t>Dipl.-Ing. (FH) Markus Ebert</t>
         </is>
       </c>
       <c r="E96" s="116" t="n"/>
@@ -3766,7 +4861,7 @@
       <c r="C98" s="68" t="n"/>
       <c r="D98" s="87" t="inlineStr">
         <is>
-          <t>Umfassende Sanierung eines belegten Klinikgebäudes inkl. Stationsmodernisierung, Erneuerung der technischen Infrastruktur, Brandabschnitte.</t>
+          <t>Umfassende Sanierung eines belegten Klinikgebäudes, inkl. Stationsmodernisierung, Erneuerung der technischen Infrastruktur, Brandabschnitte, Entrauchungskoordination, medizinische Gasschnittstellen und verbesserte Energieeffizienz.</t>
         </is>
       </c>
       <c r="E98" s="116" t="n"/>
@@ -3806,7 +4901,7 @@
       <c r="C100" s="72" t="n"/>
       <c r="D100" s="88" t="inlineStr">
         <is>
-          <t>Ausführung im laufenden Krankenhausbetrieb, komplexe Interimsversorgungskonzepte, Schadstoffsanierung</t>
+          <t>Ausführung im laufenden Krankenhausbetrieb, komplexe Interimskonzepte, Brandschutz- und TGA-Koordination, selektive Schadstoffsanierung</t>
         </is>
       </c>
       <c r="E100" s="116" t="n"/>
@@ -3901,7 +4996,7 @@
       </c>
       <c r="E104" s="124" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F104" s="125" t="n"/>
@@ -4044,4 +5139,285 @@
     <brk id="24" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100FD2288C1ADB2F847B1D9EEF9CCFE93D0" ma:contentTypeVersion="13" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="ed515cc4af5c4baac9cb51bb261367c3">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01" xmlns:ns3="71d47c0a-344d-4988-96b4-a2d0260daef6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53292e8f766ab3d0c3291e887ed8a124" ns2:_="" ns3:_="">
+    <xsd:import namespace="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01"/>
+    <xsd:import namespace="71d47c0a-344d-4988-96b4-a2d0260daef6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="15" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b53ef45f-9af6-4b32-973b-de5a9ec09512}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="71d47c0a-344d-4988-96b4-a2d0260daef6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f062de6b-3cc8-44f9-9bbc-a99a3b1e3daa" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71d47c0a-344d-4988-96b4-a2d0260daef6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532CC951-DBB4-4C9E-80F2-49778F8D5E79}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01"/>
+    <ds:schemaRef ds:uri="71d47c0a-344d-4988-96b4-a2d0260daef6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9F647E2-3436-490A-956F-1E2CD616BA72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B9DA055-B191-4F30-96D4-E3CA290A476E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71d47c0a-344d-4988-96b4-a2d0260daef6"/>
+    <ds:schemaRef ds:uri="de2b0ea1-6e8d-4dbc-a910-9c5e77483a01"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>